--- a/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 5,73</t>
+          <t>-20,01; 5,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 10,32</t>
+          <t>-27,18; 9,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 6,86</t>
+          <t>-18,62; 5,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 8,36</t>
+          <t>-19,56; 8,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 2,4</t>
+          <t>-15,76; 2,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 4,36</t>
+          <t>-19,92; 4,11</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 8,86</t>
+          <t>-26,63; 8,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 15,01</t>
+          <t>-38,01; 13,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 10,23</t>
+          <t>-24,86; 7,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 12,72</t>
+          <t>-26,49; 12,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 3,67</t>
+          <t>-21,59; 4,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 6,43</t>
+          <t>-27,59; 5,93</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,88; -9,05</t>
+          <t>-19,36; -8,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 7,42</t>
+          <t>-5,35; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -4,34</t>
+          <t>-14,66; -4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 4,58</t>
+          <t>-7,86; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -8,32</t>
+          <t>-15,48; -7,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 3,91</t>
+          <t>-4,49; 4,2</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -13,82</t>
+          <t>-27,35; -13,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 11,36</t>
+          <t>-7,66; 11,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -6,89</t>
+          <t>-21,85; -7,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 7,33</t>
+          <t>-11,82; 8,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -12,83</t>
+          <t>-23,0; -12,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 6,06</t>
+          <t>-6,63; 6,47</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,26; -0,99</t>
+          <t>-17,92; -0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 2,72</t>
+          <t>-16,26; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 1,41</t>
+          <t>-15,71; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 0,96</t>
+          <t>-15,66; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -1,81</t>
+          <t>-13,95; -2,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -0,69</t>
+          <t>-13,64; -0,47</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -2,14</t>
+          <t>-32,99; -0,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 6,07</t>
+          <t>-29,76; 8,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 3,3</t>
+          <t>-28,78; 4,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 1,99</t>
+          <t>-29,94; 4,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,46; -3,89</t>
+          <t>-26,5; -4,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,22; -1,47</t>
+          <t>-25,38; -0,96</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -7,9</t>
+          <t>-16,5; -7,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,17</t>
+          <t>-6,66; 4,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -5,1</t>
+          <t>-13,63; -4,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,37</t>
+          <t>-8,74; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -7,83</t>
+          <t>-13,67; -7,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,16</t>
+          <t>-6,45; 0,95</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -12,66</t>
+          <t>-24,84; -12,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 6,58</t>
+          <t>-10,05; 7,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,58; -8,51</t>
+          <t>-21,36; -8,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 2,35</t>
+          <t>-13,57; 1,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -12,69</t>
+          <t>-21,29; -12,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 1,91</t>
+          <t>-10,02; 1,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 5,85</t>
+          <t>-19,67; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 9,22</t>
+          <t>-26,29; 9,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 5,1</t>
+          <t>-18,8; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 8,45</t>
+          <t>-19,8; 8,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 2,79</t>
+          <t>-15,64; 3,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 4,11</t>
+          <t>-18,73; 4,52</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 8,79</t>
+          <t>-26,76; 7,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 13,23</t>
+          <t>-35,94; 14,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 7,67</t>
+          <t>-24,33; 11,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 12,45</t>
+          <t>-26,43; 12,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 4,1</t>
+          <t>-21,15; 5,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 5,93</t>
+          <t>-25,45; 6,36</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -8,87</t>
+          <t>-19,48; -9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,38</t>
+          <t>-5,13; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -4,51</t>
+          <t>-15,36; -4,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 5,1</t>
+          <t>-7,51; 5,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -7,89</t>
+          <t>-15,3; -8,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,2</t>
+          <t>-4,7; 3,73</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -13,26</t>
+          <t>-27,52; -14,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 11,16</t>
+          <t>-7,24; 11,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -7,32</t>
+          <t>-22,89; -7,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 8,15</t>
+          <t>-11,45; 8,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -12,34</t>
+          <t>-22,56; -12,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 6,47</t>
+          <t>-6,85; 5,81</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -0,3</t>
+          <t>-18,22; -0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 3,59</t>
+          <t>-15,21; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 2,15</t>
+          <t>-15,49; 2,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 1,75</t>
+          <t>-17,49; 0,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,95; -2,06</t>
+          <t>-14,49; -2,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -0,47</t>
+          <t>-13,49; -0,15</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -0,28</t>
+          <t>-33,86; -1,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 8,53</t>
+          <t>-28,59; 6,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 4,69</t>
+          <t>-29,31; 4,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 4,0</t>
+          <t>-31,51; 1,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -4,58</t>
+          <t>-27,51; -4,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,38; -0,96</t>
+          <t>-26,38; -0,5</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,96</t>
+          <t>-16,94; -8,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,49</t>
+          <t>-6,77; 4,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -4,89</t>
+          <t>-13,44; -5,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 1,16</t>
+          <t>-8,64; 1,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -7,61</t>
+          <t>-13,79; -7,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,95</t>
+          <t>-6,04; 0,97</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -12,81</t>
+          <t>-25,55; -12,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 7,34</t>
+          <t>-10,11; 6,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -8,27</t>
+          <t>-21,07; -8,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 1,91</t>
+          <t>-13,65; 2,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -12,34</t>
+          <t>-21,27; -12,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,56</t>
+          <t>-9,33; 1,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Estudios-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-7,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,89</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-1,34</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 5,12</t>
+          <t>-19,33; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 9,9</t>
+          <t>-19,7; 9,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 7,57</t>
+          <t>-19,81; 5,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 8,29</t>
+          <t>-10,94; 15,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 3,42</t>
+          <t>-14,96; 2,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 4,52</t>
+          <t>-12,23; 8,29</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-8,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-6,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-10,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-8,76%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,21%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,18%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,85%</t>
+          <t>-1,88%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 7,14</t>
+          <t>-25,62; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 14,03</t>
+          <t>-26,47; 14,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 11,36</t>
+          <t>-26,05; 8,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 12,54</t>
+          <t>-14,53; 24,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 5,12</t>
+          <t>-20,2; 3,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 6,36</t>
+          <t>-16,59; 12,27</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-9,71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-14,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -9,36</t>
+          <t>-14,47; -4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,64</t>
+          <t>-5,26; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -4,35</t>
+          <t>-18,88; -9,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 5,35</t>
+          <t>-6,1; 3,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -8,09</t>
+          <t>-15,69; -8,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,73</t>
+          <t>-3,91; 3,91</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-15,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-20,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-15,06%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,32%</t>
+          <t>-1,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,62%</t>
+          <t>-0,1%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -14,11</t>
+          <t>-21,85; -6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 11,64</t>
+          <t>-7,88; 9,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -7,16</t>
+          <t>-27,27; -13,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 8,6</t>
+          <t>-8,63; 6,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -12,47</t>
+          <t>-23,08; -12,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 5,81</t>
+          <t>-5,82; 5,99</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-6,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-9,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-6,23</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,6</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,53</t>
+          <t>-5,65</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,98</t>
+          <t>-5,86</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -0,9</t>
+          <t>-16,1; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 3,04</t>
+          <t>-15,19; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 2,58</t>
+          <t>-18,26; -0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 0,73</t>
+          <t>-16,55; 3,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -2,24</t>
+          <t>-13,9; -1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -0,15</t>
+          <t>-12,44; 0,45</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-13,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-18,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-12,43%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-13,38%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-15,28%</t>
+          <t>-11,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,05%</t>
+          <t>-11,8%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -1,92</t>
+          <t>-29,05; 3,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 6,9</t>
+          <t>-28,39; 5,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 4,98</t>
+          <t>-32,68; -2,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 1,64</t>
+          <t>-29,99; 7,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,51; -4,73</t>
+          <t>-26,46; -3,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,38; -0,5</t>
+          <t>-23,7; 0,98</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-12,62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,05</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-1,86</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -8,03</t>
+          <t>-13,1; -5,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 4,34</t>
+          <t>-7,0; 2,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -5,0</t>
+          <t>-16,72; -7,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 1,47</t>
+          <t>-5,99; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -7,62</t>
+          <t>-13,67; -7,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 0,97</t>
+          <t>-5,22; 1,48</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-14,65%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-19,61%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-2,66%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-14,65%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,19%</t>
+          <t>-2,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>-2,95%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,55; -12,95</t>
+          <t>-20,58; -8,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 6,92</t>
+          <t>-11,02; 4,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -8,32</t>
+          <t>-25,27; -12,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 2,45</t>
+          <t>-9,17; 3,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,27; -12,29</t>
+          <t>-21,3; -12,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 1,59</t>
+          <t>-8,13; 2,34</t>
         </is>
       </c>
     </row>
